--- a/data/player_stat.xlsx
+++ b/data/player_stat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="911" documentId="11_C8570FC7D454268FE34010164DC06639DFA2C1EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B48D505B-068C-46AF-9BE9-8E43A49F5803}"/>
+  <xr:revisionPtr revIDLastSave="1084" documentId="11_C8570FC7D454268FE34010164DC06639DFA2C1EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B75B0E92-A7E5-49D8-BF75-E02354FFB177}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Record_Date" sheetId="17" r:id="rId1"/>
@@ -28,6 +28,7 @@
     <sheet name="W013" sheetId="19" r:id="rId13"/>
     <sheet name="W014" sheetId="20" r:id="rId14"/>
     <sheet name="W015" sheetId="21" r:id="rId15"/>
+    <sheet name="W016" sheetId="22" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="95">
   <si>
     <t>Name</t>
   </si>
@@ -328,7 +329,10 @@
     <t>หอมหอย</t>
   </si>
   <si>
-    <t>GMMFAFA</t>
+    <t>W016</t>
+  </si>
+  <si>
+    <t>DUCKs</t>
   </si>
 </sst>
 </file>
@@ -338,7 +342,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\ mmmm\ yyyy"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -365,6 +369,13 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -402,10 +413,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -422,11 +434,33 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -779,7 +813,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5E9160B-48C2-40E4-8623-EBFD7C6323C5}">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16.77734375" style="2" bestFit="1" customWidth="1"/>
@@ -947,6 +981,17 @@
         <v>46278</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>93</v>
+      </c>
+      <c r="B16" s="5">
+        <v>46285</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>82</v>
       </c>
     </row>
@@ -2507,7 +2552,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A31">
-    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3326,7 +3371,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A31">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4145,7 +4190,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A31">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4964,7 +5009,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A31">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5397,7 +5442,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B17" s="6">
         <v>4713</v>
@@ -5789,11 +5834,840 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:H31">
     <sortCondition ref="A6:A31"/>
   </sortState>
-  <conditionalFormatting sqref="A1:A31">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  <conditionalFormatting sqref="A1:A16 A18:A31">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A17">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB79991B-F039-4808-A8AF-680AD4C61F44}">
+  <dimension ref="A1:H33"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>13</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>4</v>
+      </c>
+      <c r="H4" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B5" s="6">
+        <v>7351</v>
+      </c>
+      <c r="C5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>4</v>
+      </c>
+      <c r="H7" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>4</v>
+      </c>
+      <c r="H8" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9">
+        <v>3</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <v>4</v>
+      </c>
+      <c r="H9" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11">
+        <v>3</v>
+      </c>
+      <c r="G11">
+        <v>4</v>
+      </c>
+      <c r="H11" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12">
+        <v>5</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13">
+        <v>3</v>
+      </c>
+      <c r="E13">
+        <v>2</v>
+      </c>
+      <c r="F13">
+        <v>3</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+      <c r="H13" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14">
+        <v>4</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>90</v>
+      </c>
+      <c r="B15" s="6">
+        <v>3481</v>
+      </c>
+      <c r="C15" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15">
+        <v>5</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>4</v>
+      </c>
+      <c r="H15" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16">
+        <v>4</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>94</v>
+      </c>
+      <c r="B17" s="6">
+        <v>4713</v>
+      </c>
+      <c r="C17" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17">
+        <v>4</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>5</v>
+      </c>
+      <c r="G17">
+        <v>4</v>
+      </c>
+      <c r="H17" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B18" s="7">
+        <v>6455</v>
+      </c>
+      <c r="C18" t="s">
+        <v>63</v>
+      </c>
+      <c r="D18">
+        <v>5</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" s="6">
+        <v>2886</v>
+      </c>
+      <c r="C19" t="s">
+        <v>66</v>
+      </c>
+      <c r="D19">
+        <v>4</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>4</v>
+      </c>
+      <c r="H19" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20">
+        <v>3</v>
+      </c>
+      <c r="E20">
+        <v>2</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" t="s">
+        <v>65</v>
+      </c>
+      <c r="D21">
+        <v>3</v>
+      </c>
+      <c r="E21">
+        <v>2</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>70</v>
+      </c>
+      <c r="B22" s="7">
+        <v>168</v>
+      </c>
+      <c r="C22" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22">
+        <v>3</v>
+      </c>
+      <c r="E22">
+        <v>2</v>
+      </c>
+      <c r="F22">
+        <v>7</v>
+      </c>
+      <c r="G22">
+        <v>4</v>
+      </c>
+      <c r="H22" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>55</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23" t="s">
+        <v>64</v>
+      </c>
+      <c r="D23">
+        <v>3</v>
+      </c>
+      <c r="E23">
+        <v>2</v>
+      </c>
+      <c r="F23">
+        <v>2</v>
+      </c>
+      <c r="G23">
+        <v>4</v>
+      </c>
+      <c r="H23" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" t="s">
+        <v>66</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <v>4</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" t="s">
+        <v>66</v>
+      </c>
+      <c r="D25">
+        <v>4</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25">
+        <v>4</v>
+      </c>
+      <c r="H25" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" t="s">
+        <v>63</v>
+      </c>
+      <c r="D26">
+        <v>3</v>
+      </c>
+      <c r="E26">
+        <v>2</v>
+      </c>
+      <c r="F26">
+        <v>5</v>
+      </c>
+      <c r="G26">
+        <v>4</v>
+      </c>
+      <c r="H26" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" t="s">
+        <v>67</v>
+      </c>
+      <c r="D27">
+        <v>5</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>5</v>
+      </c>
+      <c r="G27">
+        <v>5</v>
+      </c>
+      <c r="H27" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C28" t="s">
+        <v>64</v>
+      </c>
+      <c r="D28">
+        <v>3</v>
+      </c>
+      <c r="E28">
+        <v>2</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>4</v>
+      </c>
+      <c r="H28" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C29" t="s">
+        <v>66</v>
+      </c>
+      <c r="D29">
+        <v>3</v>
+      </c>
+      <c r="E29">
+        <v>2</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" t="s">
+        <v>63</v>
+      </c>
+      <c r="D30">
+        <v>4</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30">
+        <v>7</v>
+      </c>
+      <c r="G30">
+        <v>4</v>
+      </c>
+      <c r="H30" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>22</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C31" t="s">
+        <v>65</v>
+      </c>
+      <c r="D31">
+        <v>5</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="33" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E33" s="8"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:A31">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 

--- a/data/player_stat.xlsx
+++ b/data/player_stat.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="155" documentId="11_C015F918FD5E7208B32448DBE62410048B050A7C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF7BD9C5-7127-4165-AD27-58543FEE0850}"/>
+  <xr:revisionPtr revIDLastSave="271" documentId="11_C015F918FD5E7208B32448DBE62410048B050A7C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B423B5A9-0A22-4361-8B12-002698219421}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="6" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Record_Date" sheetId="1" r:id="rId1"/>
@@ -30,13 +30,27 @@
     <sheet name="W015" sheetId="15" r:id="rId15"/>
     <sheet name="W016" sheetId="16" r:id="rId16"/>
     <sheet name="W017" sheetId="17" r:id="rId17"/>
+    <sheet name="W018" sheetId="19" r:id="rId18"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1107" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1198" uniqueCount="101">
   <si>
     <t>Name</t>
   </si>
@@ -141,9 +155,6 @@
   </si>
   <si>
     <t>5464</t>
-  </si>
-  <si>
-    <t>iCatzilla</t>
   </si>
   <si>
     <t>7449</t>
@@ -334,6 +345,15 @@
   <si>
     <t>SwallowTaiL</t>
   </si>
+  <si>
+    <t>W018</t>
+  </si>
+  <si>
+    <t>ALOHa</t>
+  </si>
+  <si>
+    <t>Catzilla</t>
+  </si>
 </sst>
 </file>
 
@@ -440,7 +460,27 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="11">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -542,6 +582,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -829,7 +873,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16.77734375" style="2" bestFit="1" customWidth="1"/>
@@ -837,189 +881,200 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" t="s">
         <v>70</v>
-      </c>
-      <c r="C1" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B2" s="5">
         <v>46187</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B3" s="5">
         <v>46194</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B4" s="5">
         <v>46201</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B5" s="5">
         <v>46208</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B6" s="5">
         <v>46215</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B7" s="5">
         <v>46222</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B8" s="5">
         <v>46229</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B9" s="5">
         <v>46236</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B10" s="5">
         <v>46243</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B11" s="5">
         <v>46250</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B12" s="5">
         <v>46257</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B13" s="5">
         <v>46264</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B14" s="5">
         <v>46271</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B15" s="5">
         <v>46278</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B16" s="5">
         <v>46285</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B17" s="5">
         <v>46292</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>98</v>
+      </c>
+      <c r="B18" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1061,10 +1116,10 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" t="s">
         <v>60</v>
-      </c>
-      <c r="B2" t="s">
-        <v>61</v>
       </c>
       <c r="C2" t="e">
         <v>#N/A</v>
@@ -1113,10 +1168,10 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" t="s">
         <v>57</v>
-      </c>
-      <c r="B4" t="s">
-        <v>58</v>
       </c>
       <c r="C4" t="e">
         <v>#N/A</v>
@@ -1139,10 +1194,10 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" t="s">
         <v>44</v>
-      </c>
-      <c r="B5" t="s">
-        <v>45</v>
       </c>
       <c r="C5" t="e">
         <v>#N/A</v>
@@ -1165,10 +1220,10 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" t="s">
         <v>51</v>
-      </c>
-      <c r="B6" t="s">
-        <v>52</v>
       </c>
       <c r="C6" t="e">
         <v>#N/A</v>
@@ -1217,10 +1272,10 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" t="s">
         <v>37</v>
-      </c>
-      <c r="B8" t="s">
-        <v>38</v>
       </c>
       <c r="C8" t="e">
         <v>#N/A</v>
@@ -1243,10 +1298,10 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" t="s">
         <v>46</v>
-      </c>
-      <c r="B9" t="s">
-        <v>47</v>
       </c>
       <c r="C9" t="e">
         <v>#N/A</v>
@@ -1269,10 +1324,10 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>88</v>
+      </c>
+      <c r="B10" t="s">
         <v>89</v>
-      </c>
-      <c r="B10" t="s">
-        <v>90</v>
       </c>
       <c r="C10" t="e">
         <v>#N/A</v>
@@ -1295,10 +1350,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" t="s">
         <v>40</v>
-      </c>
-      <c r="B11" t="s">
-        <v>41</v>
       </c>
       <c r="C11" t="e">
         <v>#N/A</v>
@@ -1321,10 +1376,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" t="s">
         <v>49</v>
-      </c>
-      <c r="B12" t="s">
-        <v>50</v>
       </c>
       <c r="C12" t="e">
         <v>#N/A</v>
@@ -1373,10 +1428,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>61</v>
+      </c>
+      <c r="B14" t="s">
         <v>62</v>
-      </c>
-      <c r="B14" t="s">
-        <v>63</v>
       </c>
       <c r="C14" t="e">
         <v>#N/A</v>
@@ -1425,10 +1480,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>66</v>
+      </c>
+      <c r="B16" t="s">
         <v>67</v>
-      </c>
-      <c r="B16" t="s">
-        <v>68</v>
       </c>
       <c r="C16" t="e">
         <v>#N/A</v>
@@ -1503,10 +1558,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" t="s">
         <v>53</v>
-      </c>
-      <c r="B19" t="s">
-        <v>54</v>
       </c>
       <c r="C19" t="e">
         <v>#N/A</v>
@@ -1555,10 +1610,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>64</v>
+      </c>
+      <c r="B21" t="s">
         <v>65</v>
-      </c>
-      <c r="B21" t="s">
-        <v>66</v>
       </c>
       <c r="C21" t="e">
         <v>#N/A</v>
@@ -1581,10 +1636,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>100</v>
+      </c>
+      <c r="B22" t="s">
         <v>35</v>
-      </c>
-      <c r="B22" t="s">
-        <v>36</v>
       </c>
       <c r="C22" t="e">
         <v>#N/A</v>
@@ -1607,10 +1662,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>54</v>
+      </c>
+      <c r="B23" t="s">
         <v>55</v>
-      </c>
-      <c r="B23" t="s">
-        <v>56</v>
       </c>
       <c r="C23" t="e">
         <v>#N/A</v>
@@ -1737,10 +1792,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B28" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C28" t="e">
         <v>#N/A</v>
@@ -2033,10 +2088,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>100</v>
+      </c>
+      <c r="B11" t="s">
         <v>35</v>
-      </c>
-      <c r="B11" t="s">
-        <v>36</v>
       </c>
       <c r="C11" t="s">
         <v>23</v>
@@ -2059,10 +2114,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" t="s">
         <v>37</v>
-      </c>
-      <c r="B12" t="s">
-        <v>38</v>
       </c>
       <c r="C12" t="s">
         <v>23</v>
@@ -2085,10 +2140,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" t="s">
         <v>40</v>
-      </c>
-      <c r="B13" t="s">
-        <v>41</v>
       </c>
       <c r="C13" t="s">
         <v>10</v>
@@ -2111,7 +2166,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B14" s="2">
         <v>7120</v>
@@ -2163,7 +2218,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B16" s="2">
         <v>6455</v>
@@ -2189,10 +2244,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" t="s">
         <v>44</v>
-      </c>
-      <c r="B17" t="s">
-        <v>45</v>
       </c>
       <c r="C17" t="s">
         <v>13</v>
@@ -2215,10 +2270,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" t="s">
         <v>46</v>
-      </c>
-      <c r="B18" t="s">
-        <v>47</v>
       </c>
       <c r="C18" t="s">
         <v>20</v>
@@ -2241,7 +2296,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B19" s="2">
         <v>168</v>
@@ -2267,10 +2322,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" t="s">
         <v>49</v>
-      </c>
-      <c r="B20" t="s">
-        <v>50</v>
       </c>
       <c r="C20" t="s">
         <v>13</v>
@@ -2293,10 +2348,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" t="s">
         <v>51</v>
-      </c>
-      <c r="B21" t="s">
-        <v>52</v>
       </c>
       <c r="C21" t="s">
         <v>23</v>
@@ -2319,10 +2374,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" t="s">
         <v>53</v>
-      </c>
-      <c r="B22" t="s">
-        <v>54</v>
       </c>
       <c r="C22" t="s">
         <v>23</v>
@@ -2345,13 +2400,13 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" t="s">
         <v>89</v>
       </c>
-      <c r="B23" t="s">
-        <v>90</v>
-      </c>
       <c r="C23" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D23">
         <v>2</v>
@@ -2371,10 +2426,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" t="s">
         <v>55</v>
-      </c>
-      <c r="B24" t="s">
-        <v>56</v>
       </c>
       <c r="C24" t="s">
         <v>10</v>
@@ -2397,10 +2452,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" t="s">
         <v>57</v>
-      </c>
-      <c r="B25" t="s">
-        <v>58</v>
       </c>
       <c r="C25" t="s">
         <v>13</v>
@@ -2423,10 +2478,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" t="s">
         <v>60</v>
-      </c>
-      <c r="B26" t="s">
-        <v>61</v>
       </c>
       <c r="C26" t="s">
         <v>13</v>
@@ -2449,10 +2504,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" t="s">
         <v>62</v>
-      </c>
-      <c r="B27" t="s">
-        <v>63</v>
       </c>
       <c r="C27" t="s">
         <v>23</v>
@@ -2475,10 +2530,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B28" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C28" t="s">
         <v>23</v>
@@ -2501,10 +2556,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>64</v>
+      </c>
+      <c r="B29" t="s">
         <v>65</v>
-      </c>
-      <c r="B29" t="s">
-        <v>66</v>
       </c>
       <c r="C29" t="s">
         <v>10</v>
@@ -2527,10 +2582,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>66</v>
+      </c>
+      <c r="B30" t="s">
         <v>67</v>
-      </c>
-      <c r="B30" t="s">
-        <v>68</v>
       </c>
       <c r="C30" t="s">
         <v>32</v>
@@ -2579,7 +2634,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A31">
-    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2852,10 +2907,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>100</v>
+      </c>
+      <c r="B11" t="s">
         <v>35</v>
-      </c>
-      <c r="B11" t="s">
-        <v>36</v>
       </c>
       <c r="C11" t="s">
         <v>23</v>
@@ -2878,10 +2933,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" t="s">
         <v>37</v>
-      </c>
-      <c r="B12" t="s">
-        <v>38</v>
       </c>
       <c r="C12" t="s">
         <v>23</v>
@@ -2904,10 +2959,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" t="s">
         <v>40</v>
-      </c>
-      <c r="B13" t="s">
-        <v>41</v>
       </c>
       <c r="C13" t="s">
         <v>13</v>
@@ -2930,7 +2985,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B14" s="2">
         <v>7120</v>
@@ -2982,7 +3037,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B16" s="2">
         <v>6455</v>
@@ -3008,10 +3063,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" t="s">
         <v>44</v>
-      </c>
-      <c r="B17" t="s">
-        <v>45</v>
       </c>
       <c r="C17" t="s">
         <v>10</v>
@@ -3034,10 +3089,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" t="s">
         <v>46</v>
-      </c>
-      <c r="B18" t="s">
-        <v>47</v>
       </c>
       <c r="C18" t="s">
         <v>20</v>
@@ -3060,7 +3115,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B19" s="2">
         <v>168</v>
@@ -3086,10 +3141,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" t="s">
         <v>49</v>
-      </c>
-      <c r="B20" t="s">
-        <v>50</v>
       </c>
       <c r="C20" t="s">
         <v>23</v>
@@ -3112,10 +3167,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" t="s">
         <v>51</v>
-      </c>
-      <c r="B21" t="s">
-        <v>52</v>
       </c>
       <c r="C21" t="s">
         <v>23</v>
@@ -3138,10 +3193,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" t="s">
         <v>53</v>
-      </c>
-      <c r="B22" t="s">
-        <v>54</v>
       </c>
       <c r="C22" t="s">
         <v>23</v>
@@ -3164,10 +3219,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" t="s">
         <v>89</v>
-      </c>
-      <c r="B23" t="s">
-        <v>90</v>
       </c>
       <c r="C23" t="s">
         <v>20</v>
@@ -3190,10 +3245,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" t="s">
         <v>55</v>
-      </c>
-      <c r="B24" t="s">
-        <v>56</v>
       </c>
       <c r="C24" t="s">
         <v>10</v>
@@ -3216,10 +3271,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" t="s">
         <v>57</v>
-      </c>
-      <c r="B25" t="s">
-        <v>58</v>
       </c>
       <c r="C25" t="s">
         <v>13</v>
@@ -3242,10 +3297,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" t="s">
         <v>60</v>
-      </c>
-      <c r="B26" t="s">
-        <v>61</v>
       </c>
       <c r="C26" t="s">
         <v>13</v>
@@ -3268,10 +3323,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" t="s">
         <v>62</v>
-      </c>
-      <c r="B27" t="s">
-        <v>63</v>
       </c>
       <c r="C27" t="s">
         <v>23</v>
@@ -3294,10 +3349,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B28" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C28" t="s">
         <v>23</v>
@@ -3320,10 +3375,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>64</v>
+      </c>
+      <c r="B29" t="s">
         <v>65</v>
-      </c>
-      <c r="B29" t="s">
-        <v>66</v>
       </c>
       <c r="C29" t="s">
         <v>10</v>
@@ -3346,10 +3401,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>66</v>
+      </c>
+      <c r="B30" t="s">
         <v>67</v>
-      </c>
-      <c r="B30" t="s">
-        <v>68</v>
       </c>
       <c r="C30" t="s">
         <v>32</v>
@@ -3398,7 +3453,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A31">
-    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3671,10 +3726,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>100</v>
+      </c>
+      <c r="B11" t="s">
         <v>35</v>
-      </c>
-      <c r="B11" t="s">
-        <v>36</v>
       </c>
       <c r="C11" t="s">
         <v>23</v>
@@ -3697,10 +3752,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" t="s">
         <v>37</v>
-      </c>
-      <c r="B12" t="s">
-        <v>38</v>
       </c>
       <c r="C12" t="s">
         <v>23</v>
@@ -3723,10 +3778,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" t="s">
         <v>40</v>
-      </c>
-      <c r="B13" t="s">
-        <v>41</v>
       </c>
       <c r="C13" t="s">
         <v>13</v>
@@ -3749,7 +3804,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B14" s="2">
         <v>7120</v>
@@ -3801,7 +3856,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B16" s="2">
         <v>6455</v>
@@ -3827,10 +3882,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" t="s">
         <v>44</v>
-      </c>
-      <c r="B17" t="s">
-        <v>45</v>
       </c>
       <c r="C17" t="s">
         <v>23</v>
@@ -3853,10 +3908,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" t="s">
         <v>46</v>
-      </c>
-      <c r="B18" t="s">
-        <v>47</v>
       </c>
       <c r="C18" t="s">
         <v>20</v>
@@ -3879,7 +3934,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B19" s="2">
         <v>168</v>
@@ -3905,10 +3960,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" t="s">
         <v>49</v>
-      </c>
-      <c r="B20" t="s">
-        <v>50</v>
       </c>
       <c r="C20" t="s">
         <v>23</v>
@@ -3931,10 +3986,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" t="s">
         <v>51</v>
-      </c>
-      <c r="B21" t="s">
-        <v>52</v>
       </c>
       <c r="C21" t="s">
         <v>23</v>
@@ -3957,10 +4012,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" t="s">
         <v>53</v>
-      </c>
-      <c r="B22" t="s">
-        <v>54</v>
       </c>
       <c r="C22" t="s">
         <v>23</v>
@@ -3983,13 +4038,13 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" t="s">
         <v>89</v>
       </c>
-      <c r="B23" t="s">
-        <v>90</v>
-      </c>
       <c r="C23" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D23">
         <v>3</v>
@@ -4009,10 +4064,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" t="s">
         <v>55</v>
-      </c>
-      <c r="B24" t="s">
-        <v>56</v>
       </c>
       <c r="C24" t="s">
         <v>32</v>
@@ -4035,10 +4090,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" t="s">
         <v>57</v>
-      </c>
-      <c r="B25" t="s">
-        <v>58</v>
       </c>
       <c r="C25" t="s">
         <v>13</v>
@@ -4061,10 +4116,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" t="s">
         <v>60</v>
-      </c>
-      <c r="B26" t="s">
-        <v>61</v>
       </c>
       <c r="C26" t="s">
         <v>13</v>
@@ -4087,10 +4142,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" t="s">
         <v>62</v>
-      </c>
-      <c r="B27" t="s">
-        <v>63</v>
       </c>
       <c r="C27" t="s">
         <v>23</v>
@@ -4113,10 +4168,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B28" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C28" t="s">
         <v>23</v>
@@ -4139,10 +4194,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>64</v>
+      </c>
+      <c r="B29" t="s">
         <v>65</v>
-      </c>
-      <c r="B29" t="s">
-        <v>66</v>
       </c>
       <c r="C29" t="s">
         <v>10</v>
@@ -4165,10 +4220,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>66</v>
+      </c>
+      <c r="B30" t="s">
         <v>67</v>
-      </c>
-      <c r="B30" t="s">
-        <v>68</v>
       </c>
       <c r="C30" t="s">
         <v>13</v>
@@ -4217,7 +4272,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A31">
-    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4542,10 +4597,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B13" t="s">
         <v>35</v>
-      </c>
-      <c r="B13" t="s">
-        <v>36</v>
       </c>
       <c r="C13" t="s">
         <v>23</v>
@@ -4568,10 +4623,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" t="s">
         <v>37</v>
-      </c>
-      <c r="B14" t="s">
-        <v>38</v>
       </c>
       <c r="C14" t="s">
         <v>23</v>
@@ -4594,7 +4649,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B15">
         <v>3481</v>
@@ -4620,10 +4675,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" t="s">
         <v>40</v>
-      </c>
-      <c r="B16" t="s">
-        <v>41</v>
       </c>
       <c r="C16" t="s">
         <v>13</v>
@@ -4646,7 +4701,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B17" s="2">
         <v>6455</v>
@@ -4672,7 +4727,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B18">
         <v>2886</v>
@@ -4698,10 +4753,10 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" t="s">
         <v>44</v>
-      </c>
-      <c r="B19" t="s">
-        <v>45</v>
       </c>
       <c r="C19" t="s">
         <v>23</v>
@@ -4724,10 +4779,10 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" t="s">
         <v>46</v>
-      </c>
-      <c r="B20" t="s">
-        <v>47</v>
       </c>
       <c r="C20" t="s">
         <v>20</v>
@@ -4750,7 +4805,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B21" s="2">
         <v>168</v>
@@ -4776,10 +4831,10 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" t="s">
         <v>49</v>
-      </c>
-      <c r="B22" t="s">
-        <v>50</v>
       </c>
       <c r="C22" t="s">
         <v>23</v>
@@ -4802,10 +4857,10 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" t="s">
         <v>51</v>
-      </c>
-      <c r="B23" t="s">
-        <v>52</v>
       </c>
       <c r="C23" t="s">
         <v>23</v>
@@ -4828,10 +4883,10 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" t="s">
         <v>53</v>
-      </c>
-      <c r="B24" t="s">
-        <v>54</v>
       </c>
       <c r="C24" t="s">
         <v>23</v>
@@ -4854,10 +4909,10 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" t="s">
         <v>55</v>
-      </c>
-      <c r="B25" t="s">
-        <v>56</v>
       </c>
       <c r="C25" t="s">
         <v>32</v>
@@ -4878,15 +4933,15 @@
         <v>#N/A</v>
       </c>
       <c r="K25" t="s">
-        <v>35</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" t="s">
         <v>57</v>
-      </c>
-      <c r="B26" t="s">
-        <v>58</v>
       </c>
       <c r="C26" t="s">
         <v>13</v>
@@ -4907,15 +4962,15 @@
         <v>#N/A</v>
       </c>
       <c r="K26" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>59</v>
+      </c>
+      <c r="B27" t="s">
         <v>60</v>
-      </c>
-      <c r="B27" t="s">
-        <v>61</v>
       </c>
       <c r="C27" t="s">
         <v>13</v>
@@ -4938,10 +4993,10 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>61</v>
+      </c>
+      <c r="B28" t="s">
         <v>62</v>
-      </c>
-      <c r="B28" t="s">
-        <v>63</v>
       </c>
       <c r="C28" t="s">
         <v>23</v>
@@ -4964,10 +5019,10 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B29" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C29" t="s">
         <v>23</v>
@@ -4990,10 +5045,10 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>64</v>
+      </c>
+      <c r="B30" t="s">
         <v>65</v>
-      </c>
-      <c r="B30" t="s">
-        <v>66</v>
       </c>
       <c r="C30" t="s">
         <v>10</v>
@@ -5016,10 +5071,10 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>66</v>
+      </c>
+      <c r="B31" t="s">
         <v>67</v>
-      </c>
-      <c r="B31" t="s">
-        <v>68</v>
       </c>
       <c r="C31" t="s">
         <v>13</v>
@@ -5042,10 +5097,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A31">
-    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25:K26">
-    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5166,7 +5221,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B5" s="6">
         <v>7351</v>
@@ -5302,7 +5357,7 @@
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D10">
         <v>4</v>
@@ -5374,10 +5429,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>35</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>36</v>
       </c>
       <c r="C13" t="s">
         <v>23</v>
@@ -5400,10 +5455,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>37</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>38</v>
       </c>
       <c r="C14" t="s">
         <v>23</v>
@@ -5426,7 +5481,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B15" s="6">
         <v>3481</v>
@@ -5452,10 +5507,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>40</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>41</v>
       </c>
       <c r="C16" t="s">
         <v>32</v>
@@ -5478,7 +5533,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B17" s="6">
         <v>4713</v>
@@ -5504,7 +5559,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B18" s="7">
         <v>6455</v>
@@ -5530,7 +5585,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B19" s="6">
         <v>2886</v>
@@ -5556,10 +5611,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="6" t="s">
         <v>44</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>45</v>
       </c>
       <c r="C20" t="s">
         <v>13</v>
@@ -5582,10 +5637,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="6" t="s">
         <v>46</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>47</v>
       </c>
       <c r="C21" t="s">
         <v>20</v>
@@ -5608,7 +5663,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B22" s="7">
         <v>168</v>
@@ -5634,10 +5689,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>49</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>50</v>
       </c>
       <c r="C23" t="s">
         <v>13</v>
@@ -5660,10 +5715,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24" s="6" t="s">
         <v>51</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>52</v>
       </c>
       <c r="C24" t="s">
         <v>23</v>
@@ -5686,10 +5741,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="C25" t="s">
         <v>23</v>
@@ -5712,10 +5767,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>54</v>
+      </c>
+      <c r="B26" s="6" t="s">
         <v>55</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>56</v>
       </c>
       <c r="C26" t="s">
         <v>10</v>
@@ -5738,10 +5793,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>56</v>
+      </c>
+      <c r="B27" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>58</v>
       </c>
       <c r="C27" t="s">
         <v>32</v>
@@ -5764,10 +5819,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>59</v>
+      </c>
+      <c r="B28" s="6" t="s">
         <v>60</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>61</v>
       </c>
       <c r="C28" t="s">
         <v>10</v>
@@ -5790,10 +5845,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C29" t="s">
         <v>23</v>
@@ -5816,10 +5871,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>64</v>
+      </c>
+      <c r="B30" s="6" t="s">
         <v>65</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>66</v>
       </c>
       <c r="C30" t="s">
         <v>10</v>
@@ -5842,10 +5897,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>66</v>
+      </c>
+      <c r="B31" s="6" t="s">
         <v>67</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>68</v>
       </c>
       <c r="C31" t="s">
         <v>20</v>
@@ -5868,10 +5923,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A16 A18:A31">
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -5993,7 +6048,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B5" s="6">
         <v>7351</v>
@@ -6129,7 +6184,7 @@
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D10">
         <v>3</v>
@@ -6201,10 +6256,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>35</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>36</v>
       </c>
       <c r="C13" t="s">
         <v>23</v>
@@ -6227,10 +6282,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>37</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>38</v>
       </c>
       <c r="C14" t="s">
         <v>23</v>
@@ -6253,7 +6308,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B15" s="6">
         <v>3481</v>
@@ -6279,10 +6334,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>40</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>41</v>
       </c>
       <c r="C16" t="s">
         <v>32</v>
@@ -6305,7 +6360,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B17" s="6">
         <v>4713</v>
@@ -6331,7 +6386,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B18" s="7">
         <v>6455</v>
@@ -6357,7 +6412,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B19" s="6">
         <v>2886</v>
@@ -6383,10 +6438,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="6" t="s">
         <v>44</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>45</v>
       </c>
       <c r="C20" t="s">
         <v>13</v>
@@ -6409,10 +6464,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="6" t="s">
         <v>46</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>47</v>
       </c>
       <c r="C21" t="s">
         <v>20</v>
@@ -6435,7 +6490,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B22" s="7">
         <v>168</v>
@@ -6461,10 +6516,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>49</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>50</v>
       </c>
       <c r="C23" t="s">
         <v>13</v>
@@ -6487,10 +6542,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24" s="6" t="s">
         <v>51</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>52</v>
       </c>
       <c r="C24" t="s">
         <v>23</v>
@@ -6513,10 +6568,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="C25" t="s">
         <v>23</v>
@@ -6539,10 +6594,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>54</v>
+      </c>
+      <c r="B26" s="6" t="s">
         <v>55</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>56</v>
       </c>
       <c r="C26" t="s">
         <v>10</v>
@@ -6565,10 +6620,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>56</v>
+      </c>
+      <c r="B27" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>58</v>
       </c>
       <c r="C27" t="s">
         <v>32</v>
@@ -6591,10 +6646,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>59</v>
+      </c>
+      <c r="B28" s="6" t="s">
         <v>60</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>61</v>
       </c>
       <c r="C28" t="s">
         <v>13</v>
@@ -6617,10 +6672,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C29" t="s">
         <v>23</v>
@@ -6643,10 +6698,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>64</v>
+      </c>
+      <c r="B30" s="6" t="s">
         <v>65</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>66</v>
       </c>
       <c r="C30" t="s">
         <v>10</v>
@@ -6669,10 +6724,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>66</v>
+      </c>
+      <c r="B31" s="6" t="s">
         <v>67</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>68</v>
       </c>
       <c r="C31" t="s">
         <v>20</v>
@@ -6698,7 +6753,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A31">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6815,7 +6870,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B5" s="6">
         <v>7351</v>
@@ -6971,10 +7026,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>37</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>38</v>
       </c>
       <c r="C11" t="s">
         <v>23</v>
@@ -6997,7 +7052,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B12" s="6">
         <v>3481</v>
@@ -7023,10 +7078,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>40</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>41</v>
       </c>
       <c r="C13" t="s">
         <v>32</v>
@@ -7049,7 +7104,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B14" s="6">
         <v>4713</v>
@@ -7075,7 +7130,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B15" s="6">
         <v>5055</v>
@@ -7101,10 +7156,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>100</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>35</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>36</v>
       </c>
       <c r="C16" t="s">
         <v>23</v>
@@ -7127,7 +7182,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B17" s="7">
         <v>6455</v>
@@ -7153,7 +7208,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B18" s="6">
         <v>2886</v>
@@ -7179,10 +7234,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>44</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>45</v>
       </c>
       <c r="C19" t="s">
         <v>10</v>
@@ -7205,10 +7260,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="6" t="s">
         <v>46</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>47</v>
       </c>
       <c r="C20" t="s">
         <v>20</v>
@@ -7231,7 +7286,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B21" s="6">
         <v>862</v>
@@ -7257,7 +7312,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B22" s="7">
         <v>168</v>
@@ -7283,10 +7338,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>49</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>50</v>
       </c>
       <c r="C23" t="s">
         <v>23</v>
@@ -7309,10 +7364,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="C24" t="s">
         <v>23</v>
@@ -7335,10 +7390,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" s="6" t="s">
         <v>55</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>56</v>
       </c>
       <c r="C25" t="s">
         <v>13</v>
@@ -7361,10 +7416,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>58</v>
       </c>
       <c r="C26" t="s">
         <v>32</v>
@@ -7387,10 +7442,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>59</v>
+      </c>
+      <c r="B27" s="6" t="s">
         <v>60</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>61</v>
       </c>
       <c r="C27" t="s">
         <v>23</v>
@@ -7413,13 +7468,13 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C28" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D28">
         <v>5</v>
@@ -7439,7 +7494,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B29" s="6">
         <v>2187</v>
@@ -7465,10 +7520,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>64</v>
+      </c>
+      <c r="B30" s="6" t="s">
         <v>65</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>66</v>
       </c>
       <c r="C30" t="s">
         <v>13</v>
@@ -7491,10 +7546,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>66</v>
+      </c>
+      <c r="B31" s="6" t="s">
         <v>67</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>68</v>
       </c>
       <c r="C31" t="s">
         <v>20</v>
@@ -7520,7 +7575,829 @@
     <sortCondition ref="A31"/>
   </sortState>
   <conditionalFormatting sqref="A1:A31">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6B298E0-F253-4558-AE36-2F661956680B}">
+  <dimension ref="A1:H31"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2">
+        <v>4</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4">
+        <v>4</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B5" s="6">
+        <v>7351</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="6">
+        <v>6654</v>
+      </c>
+      <c r="C6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="6">
+        <v>7510</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8">
+        <v>4</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11">
+        <v>5</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12">
+        <v>5</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13">
+        <v>4</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>5</v>
+      </c>
+      <c r="G13">
+        <v>4</v>
+      </c>
+      <c r="H13" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14">
+        <v>5</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>93</v>
+      </c>
+      <c r="B15" s="6">
+        <v>4713</v>
+      </c>
+      <c r="C15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15">
+        <v>5</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>4</v>
+      </c>
+      <c r="H15" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>95</v>
+      </c>
+      <c r="B16" s="6">
+        <v>5055</v>
+      </c>
+      <c r="C16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16">
+        <v>5</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>3</v>
+      </c>
+      <c r="H16" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>100</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17">
+        <v>4</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>2</v>
+      </c>
+      <c r="H17" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="7">
+        <v>6455</v>
+      </c>
+      <c r="C18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18">
+        <v>5</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>2</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19">
+        <v>4</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20">
+        <v>5</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>96</v>
+      </c>
+      <c r="B21" s="6">
+        <v>862</v>
+      </c>
+      <c r="C21" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21">
+        <v>5</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>3</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="7">
+        <v>168</v>
+      </c>
+      <c r="C22" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22">
+        <v>3</v>
+      </c>
+      <c r="E22">
+        <v>2</v>
+      </c>
+      <c r="F22">
+        <v>3</v>
+      </c>
+      <c r="G22">
+        <v>4</v>
+      </c>
+      <c r="H22" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23">
+        <v>4</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24">
+        <v>3</v>
+      </c>
+      <c r="E24">
+        <v>2</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>2</v>
+      </c>
+      <c r="H24" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25">
+        <v>5</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C26" t="s">
+        <v>32</v>
+      </c>
+      <c r="D26">
+        <v>3</v>
+      </c>
+      <c r="E26">
+        <v>2</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>59</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C27" t="s">
+        <v>23</v>
+      </c>
+      <c r="D27">
+        <v>4</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="F27">
+        <v>9</v>
+      </c>
+      <c r="G27">
+        <v>4</v>
+      </c>
+      <c r="H27" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>58</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C28" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28">
+        <v>5</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>97</v>
+      </c>
+      <c r="B29" s="6">
+        <v>2187</v>
+      </c>
+      <c r="C29" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29">
+        <v>4</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>64</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C30" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30">
+        <v>4</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30">
+        <v>8</v>
+      </c>
+      <c r="G30">
+        <v>4</v>
+      </c>
+      <c r="H30" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>66</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C31" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31">
+        <v>2</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A5 A8:A31">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7559,10 +8436,10 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" t="s">
         <v>57</v>
-      </c>
-      <c r="B2" t="s">
-        <v>58</v>
       </c>
       <c r="C2" t="e">
         <v>#N/A</v>
@@ -7603,10 +8480,10 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" t="s">
         <v>46</v>
-      </c>
-      <c r="B4" t="s">
-        <v>47</v>
       </c>
       <c r="C4" t="e">
         <v>#N/A</v>
@@ -7625,10 +8502,10 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B5" t="s">
         <v>89</v>
-      </c>
-      <c r="B5" t="s">
-        <v>90</v>
       </c>
       <c r="C5" t="e">
         <v>#N/A</v>
@@ -7647,10 +8524,10 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" t="s">
         <v>40</v>
-      </c>
-      <c r="B6" t="s">
-        <v>41</v>
       </c>
       <c r="C6" t="e">
         <v>#N/A</v>
@@ -7713,10 +8590,10 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" t="s">
         <v>67</v>
-      </c>
-      <c r="B9" t="s">
-        <v>68</v>
       </c>
       <c r="C9" t="e">
         <v>#N/A</v>
@@ -7779,10 +8656,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" t="s">
         <v>65</v>
-      </c>
-      <c r="B12" t="s">
-        <v>66</v>
       </c>
       <c r="C12" t="e">
         <v>#N/A</v>
@@ -7801,10 +8678,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B13" t="s">
         <v>35</v>
-      </c>
-      <c r="B13" t="s">
-        <v>36</v>
       </c>
       <c r="C13" t="e">
         <v>#N/A</v>
@@ -7904,10 +8781,10 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" t="s">
         <v>60</v>
-      </c>
-      <c r="B2" t="s">
-        <v>61</v>
       </c>
       <c r="C2" t="e">
         <v>#N/A</v>
@@ -7926,10 +8803,10 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" t="s">
         <v>57</v>
-      </c>
-      <c r="B3" t="s">
-        <v>58</v>
       </c>
       <c r="C3" t="e">
         <v>#N/A</v>
@@ -7970,10 +8847,10 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" t="s">
         <v>46</v>
-      </c>
-      <c r="B5" t="s">
-        <v>47</v>
       </c>
       <c r="C5" t="e">
         <v>#N/A</v>
@@ -7992,10 +8869,10 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B6" t="s">
         <v>89</v>
-      </c>
-      <c r="B6" t="s">
-        <v>90</v>
       </c>
       <c r="C6" t="e">
         <v>#N/A</v>
@@ -8014,10 +8891,10 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s">
         <v>40</v>
-      </c>
-      <c r="B7" t="s">
-        <v>41</v>
       </c>
       <c r="C7" t="e">
         <v>#N/A</v>
@@ -8080,10 +8957,10 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10" t="s">
         <v>67</v>
-      </c>
-      <c r="B10" t="s">
-        <v>68</v>
       </c>
       <c r="C10" t="e">
         <v>#N/A</v>
@@ -8168,10 +9045,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" t="s">
         <v>65</v>
-      </c>
-      <c r="B14" t="s">
-        <v>66</v>
       </c>
       <c r="C14" t="e">
         <v>#N/A</v>
@@ -8190,10 +9067,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>100</v>
+      </c>
+      <c r="B15" t="s">
         <v>35</v>
-      </c>
-      <c r="B15" t="s">
-        <v>36</v>
       </c>
       <c r="C15" t="e">
         <v>#N/A</v>
@@ -8292,10 +9169,10 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" t="s">
         <v>60</v>
-      </c>
-      <c r="B2" t="s">
-        <v>61</v>
       </c>
       <c r="C2" t="e">
         <v>#N/A</v>
@@ -8314,10 +9191,10 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" t="s">
         <v>57</v>
-      </c>
-      <c r="B3" t="s">
-        <v>58</v>
       </c>
       <c r="C3" t="e">
         <v>#N/A</v>
@@ -8358,10 +9235,10 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" t="s">
         <v>46</v>
-      </c>
-      <c r="B5" t="s">
-        <v>47</v>
       </c>
       <c r="C5" t="e">
         <v>#N/A</v>
@@ -8380,10 +9257,10 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" t="s">
         <v>40</v>
-      </c>
-      <c r="B6" t="s">
-        <v>41</v>
       </c>
       <c r="C6" t="e">
         <v>#N/A</v>
@@ -8446,10 +9323,10 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" t="s">
         <v>67</v>
-      </c>
-      <c r="B9" t="s">
-        <v>68</v>
       </c>
       <c r="C9" t="e">
         <v>#N/A</v>
@@ -8534,10 +9411,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" t="s">
         <v>65</v>
-      </c>
-      <c r="B13" t="s">
-        <v>66</v>
       </c>
       <c r="C13" t="e">
         <v>#N/A</v>
@@ -8556,10 +9433,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>100</v>
+      </c>
+      <c r="B14" t="s">
         <v>35</v>
-      </c>
-      <c r="B14" t="s">
-        <v>36</v>
       </c>
       <c r="C14" t="e">
         <v>#N/A</v>
@@ -8578,10 +9455,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" t="s">
         <v>55</v>
-      </c>
-      <c r="B15" t="s">
-        <v>56</v>
       </c>
       <c r="C15" t="e">
         <v>#N/A</v>
@@ -8680,10 +9557,10 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" t="s">
         <v>60</v>
-      </c>
-      <c r="B2" t="s">
-        <v>61</v>
       </c>
       <c r="C2" t="e">
         <v>#N/A</v>
@@ -8702,10 +9579,10 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" t="s">
         <v>57</v>
-      </c>
-      <c r="B3" t="s">
-        <v>58</v>
       </c>
       <c r="C3" t="e">
         <v>#N/A</v>
@@ -8724,10 +9601,10 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" t="s">
         <v>46</v>
-      </c>
-      <c r="B4" t="s">
-        <v>47</v>
       </c>
       <c r="C4" t="e">
         <v>#N/A</v>
@@ -8746,10 +9623,10 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B5" t="s">
         <v>89</v>
-      </c>
-      <c r="B5" t="s">
-        <v>90</v>
       </c>
       <c r="C5" t="e">
         <v>#N/A</v>
@@ -8768,10 +9645,10 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" t="s">
         <v>40</v>
-      </c>
-      <c r="B6" t="s">
-        <v>41</v>
       </c>
       <c r="C6" t="e">
         <v>#N/A</v>
@@ -8834,10 +9711,10 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" t="s">
         <v>67</v>
-      </c>
-      <c r="B9" t="s">
-        <v>68</v>
       </c>
       <c r="C9" t="e">
         <v>#N/A</v>
@@ -8922,10 +9799,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" t="s">
         <v>65</v>
-      </c>
-      <c r="B13" t="s">
-        <v>66</v>
       </c>
       <c r="C13" t="e">
         <v>#N/A</v>
@@ -8944,10 +9821,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>100</v>
+      </c>
+      <c r="B14" t="s">
         <v>35</v>
-      </c>
-      <c r="B14" t="s">
-        <v>36</v>
       </c>
       <c r="C14" t="e">
         <v>#N/A</v>
@@ -8966,10 +9843,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" t="s">
         <v>55</v>
-      </c>
-      <c r="B15" t="s">
-        <v>56</v>
       </c>
       <c r="C15" t="e">
         <v>#N/A</v>
@@ -9090,10 +9967,10 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" t="s">
         <v>60</v>
-      </c>
-      <c r="B2" t="s">
-        <v>61</v>
       </c>
       <c r="C2" t="e">
         <v>#N/A</v>
@@ -9112,10 +9989,10 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" t="s">
         <v>57</v>
-      </c>
-      <c r="B3" t="s">
-        <v>58</v>
       </c>
       <c r="C3" t="e">
         <v>#N/A</v>
@@ -9156,10 +10033,10 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" t="s">
         <v>46</v>
-      </c>
-      <c r="B5" t="s">
-        <v>47</v>
       </c>
       <c r="C5" t="e">
         <v>#N/A</v>
@@ -9178,10 +10055,10 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B6" t="s">
         <v>89</v>
-      </c>
-      <c r="B6" t="s">
-        <v>90</v>
       </c>
       <c r="C6" t="e">
         <v>#N/A</v>
@@ -9200,10 +10077,10 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s">
         <v>40</v>
-      </c>
-      <c r="B7" t="s">
-        <v>41</v>
       </c>
       <c r="C7" t="e">
         <v>#N/A</v>
@@ -9266,10 +10143,10 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10" t="s">
         <v>67</v>
-      </c>
-      <c r="B10" t="s">
-        <v>68</v>
       </c>
       <c r="C10" t="e">
         <v>#N/A</v>
@@ -9354,10 +10231,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" t="s">
         <v>65</v>
-      </c>
-      <c r="B14" t="s">
-        <v>66</v>
       </c>
       <c r="C14" t="e">
         <v>#N/A</v>
@@ -9376,10 +10253,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>100</v>
+      </c>
+      <c r="B15" t="s">
         <v>35</v>
-      </c>
-      <c r="B15" t="s">
-        <v>36</v>
       </c>
       <c r="C15" t="e">
         <v>#N/A</v>
@@ -9398,10 +10275,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" t="s">
         <v>55</v>
-      </c>
-      <c r="B16" t="s">
-        <v>56</v>
       </c>
       <c r="C16" t="e">
         <v>#N/A</v>
@@ -9522,10 +10399,10 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" t="s">
         <v>60</v>
-      </c>
-      <c r="B2" t="s">
-        <v>61</v>
       </c>
       <c r="C2" t="e">
         <v>#N/A</v>
@@ -9544,10 +10421,10 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" t="s">
         <v>57</v>
-      </c>
-      <c r="B3" t="s">
-        <v>58</v>
       </c>
       <c r="C3" t="e">
         <v>#N/A</v>
@@ -9588,10 +10465,10 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" t="s">
         <v>46</v>
-      </c>
-      <c r="B5" t="s">
-        <v>47</v>
       </c>
       <c r="C5" t="e">
         <v>#N/A</v>
@@ -9610,10 +10487,10 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B6" t="s">
         <v>89</v>
-      </c>
-      <c r="B6" t="s">
-        <v>90</v>
       </c>
       <c r="C6" t="e">
         <v>#N/A</v>
@@ -9632,10 +10509,10 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s">
         <v>40</v>
-      </c>
-      <c r="B7" t="s">
-        <v>41</v>
       </c>
       <c r="C7" t="e">
         <v>#N/A</v>
@@ -9698,10 +10575,10 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10" t="s">
         <v>67</v>
-      </c>
-      <c r="B10" t="s">
-        <v>68</v>
       </c>
       <c r="C10" t="e">
         <v>#N/A</v>
@@ -9786,10 +10663,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" t="s">
         <v>65</v>
-      </c>
-      <c r="B14" t="s">
-        <v>66</v>
       </c>
       <c r="C14" t="e">
         <v>#N/A</v>
@@ -9808,10 +10685,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>100</v>
+      </c>
+      <c r="B15" t="s">
         <v>35</v>
-      </c>
-      <c r="B15" t="s">
-        <v>36</v>
       </c>
       <c r="C15" t="e">
         <v>#N/A</v>
@@ -9830,10 +10707,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" t="s">
         <v>55</v>
-      </c>
-      <c r="B16" t="s">
-        <v>56</v>
       </c>
       <c r="C16" t="e">
         <v>#N/A</v>
@@ -9954,10 +10831,10 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" t="s">
         <v>60</v>
-      </c>
-      <c r="B2" t="s">
-        <v>61</v>
       </c>
       <c r="C2" t="e">
         <v>#N/A</v>
@@ -9998,10 +10875,10 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" t="s">
         <v>57</v>
-      </c>
-      <c r="B4" t="s">
-        <v>58</v>
       </c>
       <c r="C4" t="e">
         <v>#N/A</v>
@@ -10020,10 +10897,10 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" t="s">
         <v>51</v>
-      </c>
-      <c r="B5" t="s">
-        <v>52</v>
       </c>
       <c r="C5" t="e">
         <v>#N/A</v>
@@ -10064,10 +10941,10 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" t="s">
         <v>46</v>
-      </c>
-      <c r="B7" t="s">
-        <v>47</v>
       </c>
       <c r="C7" t="e">
         <v>#N/A</v>
@@ -10086,10 +10963,10 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8" t="s">
         <v>89</v>
-      </c>
-      <c r="B8" t="s">
-        <v>90</v>
       </c>
       <c r="C8" t="e">
         <v>#N/A</v>
@@ -10108,10 +10985,10 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" t="s">
         <v>40</v>
-      </c>
-      <c r="B9" t="s">
-        <v>41</v>
       </c>
       <c r="C9" t="e">
         <v>#N/A</v>
@@ -10174,10 +11051,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" t="s">
         <v>67</v>
-      </c>
-      <c r="B12" t="s">
-        <v>68</v>
       </c>
       <c r="C12" t="e">
         <v>#N/A</v>
@@ -10262,10 +11139,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16" t="s">
         <v>65</v>
-      </c>
-      <c r="B16" t="s">
-        <v>66</v>
       </c>
       <c r="C16" t="e">
         <v>#N/A</v>
@@ -10284,10 +11161,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>100</v>
+      </c>
+      <c r="B17" t="s">
         <v>35</v>
-      </c>
-      <c r="B17" t="s">
-        <v>36</v>
       </c>
       <c r="C17" t="e">
         <v>#N/A</v>
@@ -10306,10 +11183,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" t="s">
         <v>55</v>
-      </c>
-      <c r="B18" t="s">
-        <v>56</v>
       </c>
       <c r="C18" t="e">
         <v>#N/A</v>
@@ -10394,10 +11271,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B22" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C22" t="e">
         <v>#N/A</v>
@@ -10452,10 +11329,10 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" t="s">
         <v>60</v>
-      </c>
-      <c r="B2" t="s">
-        <v>61</v>
       </c>
       <c r="C2" t="e">
         <v>#N/A</v>
@@ -10504,10 +11381,10 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" t="s">
         <v>57</v>
-      </c>
-      <c r="B4" t="s">
-        <v>58</v>
       </c>
       <c r="C4" t="e">
         <v>#N/A</v>
@@ -10530,10 +11407,10 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" t="s">
         <v>44</v>
-      </c>
-      <c r="B5" t="s">
-        <v>45</v>
       </c>
       <c r="C5" t="e">
         <v>#N/A</v>
@@ -10556,10 +11433,10 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" t="s">
         <v>51</v>
-      </c>
-      <c r="B6" t="s">
-        <v>52</v>
       </c>
       <c r="C6" t="e">
         <v>#N/A</v>
@@ -10608,10 +11485,10 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" t="s">
         <v>37</v>
-      </c>
-      <c r="B8" t="s">
-        <v>38</v>
       </c>
       <c r="C8" t="e">
         <v>#N/A</v>
@@ -10634,10 +11511,10 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" t="s">
         <v>46</v>
-      </c>
-      <c r="B9" t="s">
-        <v>47</v>
       </c>
       <c r="C9" t="e">
         <v>#N/A</v>
@@ -10660,10 +11537,10 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>88</v>
+      </c>
+      <c r="B10" t="s">
         <v>89</v>
-      </c>
-      <c r="B10" t="s">
-        <v>90</v>
       </c>
       <c r="C10" t="e">
         <v>#N/A</v>
@@ -10686,10 +11563,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" t="s">
         <v>40</v>
-      </c>
-      <c r="B11" t="s">
-        <v>41</v>
       </c>
       <c r="C11" t="e">
         <v>#N/A</v>
@@ -10712,10 +11589,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" t="s">
         <v>49</v>
-      </c>
-      <c r="B12" t="s">
-        <v>50</v>
       </c>
       <c r="C12" t="e">
         <v>#N/A</v>
@@ -10764,10 +11641,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>61</v>
+      </c>
+      <c r="B14" t="s">
         <v>62</v>
-      </c>
-      <c r="B14" t="s">
-        <v>63</v>
       </c>
       <c r="C14" t="e">
         <v>#N/A</v>
@@ -10816,10 +11693,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>66</v>
+      </c>
+      <c r="B16" t="s">
         <v>67</v>
-      </c>
-      <c r="B16" t="s">
-        <v>68</v>
       </c>
       <c r="C16" t="e">
         <v>#N/A</v>
@@ -10894,10 +11771,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" t="s">
         <v>53</v>
-      </c>
-      <c r="B19" t="s">
-        <v>54</v>
       </c>
       <c r="C19" t="e">
         <v>#N/A</v>
@@ -10946,10 +11823,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>64</v>
+      </c>
+      <c r="B21" t="s">
         <v>65</v>
-      </c>
-      <c r="B21" t="s">
-        <v>66</v>
       </c>
       <c r="C21" t="e">
         <v>#N/A</v>
@@ -10972,10 +11849,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>100</v>
+      </c>
+      <c r="B22" t="s">
         <v>35</v>
-      </c>
-      <c r="B22" t="s">
-        <v>36</v>
       </c>
       <c r="C22" t="e">
         <v>#N/A</v>
@@ -10998,10 +11875,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>54</v>
+      </c>
+      <c r="B23" t="s">
         <v>55</v>
-      </c>
-      <c r="B23" t="s">
-        <v>56</v>
       </c>
       <c r="C23" t="e">
         <v>#N/A</v>
@@ -11102,10 +11979,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B27" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C27" t="e">
         <v>#N/A</v>

--- a/data/player_stat.xlsx
+++ b/data/player_stat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="271" documentId="11_C015F918FD5E7208B32448DBE62410048B050A7C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B423B5A9-0A22-4361-8B12-002698219421}"/>
+  <xr:revisionPtr revIDLastSave="384" documentId="11_C015F918FD5E7208B32448DBE62410048B050A7C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB851B65-8524-4995-B9CE-1988CE1C5A04}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="6" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Record_Date" sheetId="1" r:id="rId1"/>
@@ -31,6 +31,7 @@
     <sheet name="W016" sheetId="16" r:id="rId16"/>
     <sheet name="W017" sheetId="17" r:id="rId17"/>
     <sheet name="W018" sheetId="19" r:id="rId18"/>
+    <sheet name="W019" sheetId="20" r:id="rId19"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1198" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1289" uniqueCount="102">
   <si>
     <t>Name</t>
   </si>
@@ -354,6 +355,9 @@
   <si>
     <t>Catzilla</t>
   </si>
+  <si>
+    <t>W019</t>
+  </si>
 </sst>
 </file>
 
@@ -460,7 +464,27 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="13">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -873,7 +897,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16.77734375" style="2" bestFit="1" customWidth="1"/>
@@ -1075,6 +1099,17 @@
       </c>
       <c r="C18" s="2" t="s">
         <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>101</v>
+      </c>
+      <c r="B19" s="5">
+        <v>46306</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -2634,7 +2669,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A31">
-    <cfRule type="duplicateValues" dxfId="10" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3453,7 +3488,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A31">
-    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4272,7 +4307,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A31">
-    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5097,10 +5132,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A31">
-    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25:K26">
-    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5923,10 +5958,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A16 A18:A31">
-    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17">
-    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -6753,7 +6788,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A31">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7575,7 +7610,7 @@
     <sortCondition ref="A31"/>
   </sortState>
   <conditionalFormatting sqref="A1:A31">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8393,11 +8428,836 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A1:A5 A8:A31">
+    <cfRule type="duplicateValues" dxfId="3" priority="10"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61D53659-20A8-4A7B-BB98-EB09EE39CDFF}">
+  <dimension ref="A1:H31"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>4</v>
+      </c>
+      <c r="H4" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B5" s="6">
+        <v>7351</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="6">
+        <v>6654</v>
+      </c>
+      <c r="C6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="6">
+        <v>7510</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
+      </c>
+      <c r="G7">
+        <v>4</v>
+      </c>
+      <c r="H7" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>4</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10">
+        <v>4</v>
+      </c>
+      <c r="H10" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>4</v>
+      </c>
+      <c r="F11">
+        <v>6</v>
+      </c>
+      <c r="G11">
+        <v>4</v>
+      </c>
+      <c r="H11" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12">
+        <v>5</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>10</v>
+      </c>
+      <c r="G12">
+        <v>4</v>
+      </c>
+      <c r="H12" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13">
+        <v>2</v>
+      </c>
+      <c r="E13">
+        <v>3</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14">
+        <v>3</v>
+      </c>
+      <c r="E14">
+        <v>2</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>4</v>
+      </c>
+      <c r="H14" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>93</v>
+      </c>
+      <c r="B15" s="6">
+        <v>4713</v>
+      </c>
+      <c r="C15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15">
+        <v>3</v>
+      </c>
+      <c r="E15">
+        <v>2</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>4</v>
+      </c>
+      <c r="H15" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>95</v>
+      </c>
+      <c r="B16" s="6">
+        <v>5055</v>
+      </c>
+      <c r="C16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="G16">
+        <v>4</v>
+      </c>
+      <c r="H16" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>100</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17">
+        <v>2</v>
+      </c>
+      <c r="E17">
+        <v>3</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17">
+        <v>4</v>
+      </c>
+      <c r="H17" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="7">
+        <v>6455</v>
+      </c>
+      <c r="C18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18">
+        <v>3</v>
+      </c>
+      <c r="E18">
+        <v>2</v>
+      </c>
+      <c r="F18">
+        <v>9</v>
+      </c>
+      <c r="G18">
+        <v>4</v>
+      </c>
+      <c r="H18" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19">
+        <v>5</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>4</v>
+      </c>
+      <c r="H19" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>5</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>96</v>
+      </c>
+      <c r="B21" s="6">
+        <v>862</v>
+      </c>
+      <c r="C21" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21">
+        <v>2</v>
+      </c>
+      <c r="E21">
+        <v>3</v>
+      </c>
+      <c r="F21">
+        <v>3</v>
+      </c>
+      <c r="G21">
+        <v>4</v>
+      </c>
+      <c r="H21" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="7">
+        <v>168</v>
+      </c>
+      <c r="C22" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22">
+        <v>2</v>
+      </c>
+      <c r="E22">
+        <v>3</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>4</v>
+      </c>
+      <c r="H22" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23">
+        <v>2</v>
+      </c>
+      <c r="E23">
+        <v>3</v>
+      </c>
+      <c r="F23">
+        <v>4</v>
+      </c>
+      <c r="G23">
+        <v>4</v>
+      </c>
+      <c r="H23" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24">
+        <v>2</v>
+      </c>
+      <c r="E24">
+        <v>3</v>
+      </c>
+      <c r="F24">
+        <v>3</v>
+      </c>
+      <c r="G24">
+        <v>3</v>
+      </c>
+      <c r="H24" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25">
+        <v>5</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>3</v>
+      </c>
+      <c r="G25">
+        <v>4</v>
+      </c>
+      <c r="H25" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C26" t="s">
+        <v>32</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26">
+        <v>4</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>5</v>
+      </c>
+      <c r="H26" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>59</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C27" t="s">
+        <v>23</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <v>4</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>58</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C28" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28">
+        <v>3</v>
+      </c>
+      <c r="E28">
+        <v>2</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>97</v>
+      </c>
+      <c r="B29" s="6">
+        <v>2187</v>
+      </c>
+      <c r="C29" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29">
+        <v>2</v>
+      </c>
+      <c r="E29">
+        <v>3</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>64</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C30" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30">
+        <v>4</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30">
+        <v>4</v>
+      </c>
+      <c r="G30">
+        <v>4</v>
+      </c>
+      <c r="H30" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>66</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C31" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31">
+        <v>4</v>
+      </c>
+      <c r="E31">
+        <v>1</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+      <c r="H31" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+  </sheetData>
   <conditionalFormatting sqref="A1:A5 A8:A31">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A31">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/player_stat.xlsx
+++ b/data/player_stat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="384" documentId="11_C015F918FD5E7208B32448DBE62410048B050A7C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB851B65-8524-4995-B9CE-1988CE1C5A04}"/>
+  <xr:revisionPtr revIDLastSave="512" documentId="11_C015F918FD5E7208B32448DBE62410048B050A7C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23AD01F4-2479-4734-A5C4-92FBCE460DB6}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="8" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Record_Date" sheetId="1" r:id="rId1"/>
@@ -32,6 +32,7 @@
     <sheet name="W017" sheetId="17" r:id="rId17"/>
     <sheet name="W018" sheetId="19" r:id="rId18"/>
     <sheet name="W019" sheetId="20" r:id="rId19"/>
+    <sheet name="W020" sheetId="21" r:id="rId20"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -51,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1289" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1379" uniqueCount="104">
   <si>
     <t>Name</t>
   </si>
@@ -358,6 +359,12 @@
   <si>
     <t>W019</t>
   </si>
+  <si>
+    <t>W020</t>
+  </si>
+  <si>
+    <t>GGood</t>
+  </si>
 </sst>
 </file>
 
@@ -464,7 +471,27 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="15">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -897,7 +924,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16.77734375" style="2" bestFit="1" customWidth="1"/>
@@ -1110,6 +1137,17 @@
       </c>
       <c r="C19" s="2" t="s">
         <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>102</v>
+      </c>
+      <c r="B20" s="5">
+        <v>46313</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2669,7 +2707,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A31">
-    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3488,7 +3526,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A31">
-    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4307,7 +4345,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A31">
-    <cfRule type="duplicateValues" dxfId="10" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5132,10 +5170,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A31">
-    <cfRule type="duplicateValues" dxfId="9" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25:K26">
-    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5958,10 +5996,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A16 A18:A31">
-    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17">
-    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -6788,7 +6826,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A31">
-    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7610,7 +7648,7 @@
     <sortCondition ref="A31"/>
   </sortState>
   <conditionalFormatting sqref="A1:A31">
-    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8429,10 +8467,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A5 A8:A31">
-    <cfRule type="duplicateValues" dxfId="3" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9254,10 +9292,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A5 A8:A31">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:A31">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9608,6 +9646,835 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44B3ADD5-D51C-4107-8536-06483CDBA161}">
+  <dimension ref="A1:H31"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4">
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B5" s="6">
+        <v>7351</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="6">
+        <v>6654</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B8" s="6">
+        <v>7510</v>
+      </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="F8">
+        <v>6</v>
+      </c>
+      <c r="G8">
+        <v>4</v>
+      </c>
+      <c r="H8" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9">
+        <v>4</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
+      </c>
+      <c r="F10">
+        <v>6</v>
+      </c>
+      <c r="G10">
+        <v>4</v>
+      </c>
+      <c r="H10" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11">
+        <v>3</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12">
+        <v>5</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13">
+        <v>5</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14">
+        <v>4</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15">
+        <v>2</v>
+      </c>
+      <c r="E15">
+        <v>3</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>93</v>
+      </c>
+      <c r="B16" s="6">
+        <v>4713</v>
+      </c>
+      <c r="C16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16">
+        <v>5</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>95</v>
+      </c>
+      <c r="B17" s="6">
+        <v>5055</v>
+      </c>
+      <c r="C17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17">
+        <v>4</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>4</v>
+      </c>
+      <c r="H17" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>103</v>
+      </c>
+      <c r="B18" s="6">
+        <v>6612</v>
+      </c>
+      <c r="C18" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18">
+        <v>5</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="7">
+        <v>6455</v>
+      </c>
+      <c r="C19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19">
+        <v>4</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>3</v>
+      </c>
+      <c r="G19">
+        <v>4</v>
+      </c>
+      <c r="H19" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20">
+        <v>4</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>96</v>
+      </c>
+      <c r="B21" s="6">
+        <v>862</v>
+      </c>
+      <c r="C21" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21">
+        <v>4</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="7">
+        <v>168</v>
+      </c>
+      <c r="C22" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22">
+        <v>4</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>4</v>
+      </c>
+      <c r="H22" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>4</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>4</v>
+      </c>
+      <c r="H23" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24">
+        <v>4</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <v>6</v>
+      </c>
+      <c r="G24">
+        <v>4</v>
+      </c>
+      <c r="H24" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25">
+        <v>5</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C26" t="s">
+        <v>32</v>
+      </c>
+      <c r="D26">
+        <v>3</v>
+      </c>
+      <c r="E26">
+        <v>2</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>59</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C27" t="s">
+        <v>23</v>
+      </c>
+      <c r="D27">
+        <v>4</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="F27">
+        <v>2</v>
+      </c>
+      <c r="G27">
+        <v>4</v>
+      </c>
+      <c r="H27" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>58</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C28" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28">
+        <v>5</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>2</v>
+      </c>
+      <c r="G28">
+        <v>4</v>
+      </c>
+      <c r="H28" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>97</v>
+      </c>
+      <c r="B29" s="6">
+        <v>2187</v>
+      </c>
+      <c r="C29" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29">
+        <v>3</v>
+      </c>
+      <c r="E29">
+        <v>2</v>
+      </c>
+      <c r="F29">
+        <v>6</v>
+      </c>
+      <c r="G29">
+        <v>5</v>
+      </c>
+      <c r="H29" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>64</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C30" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30">
+        <v>4</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30">
+        <v>2</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>66</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C31" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31">
+        <v>4</v>
+      </c>
+      <c r="E31">
+        <v>1</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:H31">
+    <sortCondition ref="A31"/>
+  </sortState>
+  <conditionalFormatting sqref="A1:A5 A8:A31">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A31">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H17"/>
